--- a/experiments/E3_augmentation/results/results.xlsx
+++ b/experiments/E3_augmentation/results/results.xlsx
@@ -430,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>default,no_mosaic</t>
+          <t>default,no_hsv</t>
         </is>
       </c>
     </row>
@@ -574,15 +574,15 @@
   <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
@@ -590,10 +590,10 @@
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,10 +740,10 @@
         <v>5.449925</v>
       </c>
       <c r="N2" t="n">
-        <v>134.4825439666996</v>
+        <v>99.63801436685269</v>
       </c>
       <c r="O2" t="n">
-        <v>126.7023358666847</v>
+        <v>94.24334023339422</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -764,69 +764,69 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>no_mosaic</t>
+          <t>no_hsv</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mosaic off</t>
+          <t>colour jitter off (hue/saturation/value)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mosaic glues 4 photos together: not a real road scene, but adds context variety</t>
+          <t>brightness/saturation changes are realistic (light, weather); strong hue shifts are not (blue asphalt)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5206093987959717</v>
+        <v>0.5320690192742034</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2913628407137271</v>
+        <v>0.2943072632765301</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6076288085501791</v>
+        <v>0.63170670153629</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4772154064750826</v>
+        <v>0.4731630187037363</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4339497565715403</v>
+        <v>0.4401527802054898</v>
       </c>
       <c r="I3" t="n">
-        <v>0.447627996336935</v>
+        <v>0.4659027158372329</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5473966397065639</v>
+        <v>0.5557851455163011</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6534632025688476</v>
+        <v>0.6664354355377898</v>
       </c>
       <c r="L3" t="n">
         <v>2.535344</v>
       </c>
       <c r="M3" t="n">
-        <v>5.449989</v>
+        <v>5.449925</v>
       </c>
       <c r="N3" t="n">
-        <v>99.56137866665813</v>
+        <v>122.3168751000837</v>
       </c>
       <c r="O3" t="n">
-        <v>94.28941899999093</v>
+        <v>115.6812610667354</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.002506744098404456</v>
+        <v>0.008952876379827224</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.008170190946977185</v>
+        <v>-0.001967167313027707</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.001824612562049965</v>
+        <v>0.01645010693824794</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006380137050185031</v>
+        <v>0.01476864285992219</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.006412309934775484</v>
+        <v>0.006559923034166748</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E3_augmentation/results/results.xlsx
+++ b/experiments/E3_augmentation/results/results.xlsx
@@ -430,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>default,no_hsv</t>
+          <t>default,no_fliplr</t>
         </is>
       </c>
     </row>
@@ -574,25 +574,25 @@
   <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="53" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -740,10 +740,10 @@
         <v>5.449925</v>
       </c>
       <c r="N2" t="n">
-        <v>99.63801436685269</v>
+        <v>98.62145276662584</v>
       </c>
       <c r="O2" t="n">
-        <v>94.24334023339422</v>
+        <v>93.2832147666583</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -764,69 +764,69 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>no_hsv</t>
+          <t>no_fliplr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>colour jitter off (hue/saturation/value)</t>
+          <t>horizontal flip off</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>brightness/saturation changes are realistic (light, weather); strong hue shifts are not (blue asphalt)</t>
+          <t>left-right mirror is realistic (traffic side aside)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5320690192742034</v>
+        <v>0.5361405460358264</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2943072632765301</v>
+        <v>0.2991479711741394</v>
       </c>
       <c r="F3" t="n">
-        <v>0.63170670153629</v>
+        <v>0.6405576329174778</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4731630187037363</v>
+        <v>0.4821767001114827</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4401527802054898</v>
+        <v>0.4356186259061205</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4659027158372329</v>
+        <v>0.4722615630266953</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5557851455163011</v>
+        <v>0.5584525403246516</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6664354355377898</v>
+        <v>0.6782294548858383</v>
       </c>
       <c r="L3" t="n">
         <v>2.535344</v>
       </c>
       <c r="M3" t="n">
-        <v>5.449925</v>
+        <v>5.449989</v>
       </c>
       <c r="N3" t="n">
-        <v>122.3168751000837</v>
+        <v>96.82461536661624</v>
       </c>
       <c r="O3" t="n">
-        <v>115.6812610667354</v>
+        <v>91.59820200002287</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008952876379827224</v>
+        <v>0.01302440314145026</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.001967167313027707</v>
+        <v>-0.006501321612396915</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01645010693824794</v>
+        <v>0.02280895412771028</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01476864285992219</v>
+        <v>0.01743603766827273</v>
       </c>
       <c r="T3" t="n">
-        <v>0.006559923034166748</v>
+        <v>0.01835394238221522</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E3_augmentation/results/results.xlsx
+++ b/experiments/E3_augmentation/results/results.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>default,no_fliplr</t>
+          <t>default,flipud_on</t>
         </is>
       </c>
     </row>
@@ -576,23 +576,23 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="53" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -740,10 +740,10 @@
         <v>5.449925</v>
       </c>
       <c r="N2" t="n">
-        <v>98.62145276662584</v>
+        <v>96.87502849992597</v>
       </c>
       <c r="O2" t="n">
-        <v>93.2832147666583</v>
+        <v>91.63380619993404</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -764,42 +764,42 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>no_fliplr</t>
+          <t>flipud_on</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>horizontal flip off</t>
+          <t>vertical flip ON</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>left-right mirror is realistic (traffic side aside)</t>
+          <t>UNREALISTIC: the road would be upside down, the camera never sees that</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5361405460358264</v>
+        <v>0.5215041216414924</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2991479711741394</v>
+        <v>0.2875122260258314</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6405576329174778</v>
+        <v>0.6202798900142326</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4821767001114827</v>
+        <v>0.4782139192836582</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4356186259061205</v>
+        <v>0.4262987122974991</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4722615630266953</v>
+        <v>0.4520009086903073</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5584525403246516</v>
+        <v>0.5424219079827084</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6782294548858383</v>
+        <v>0.6652949575954547</v>
       </c>
       <c r="L3" t="n">
         <v>2.535344</v>
@@ -808,25 +808,25 @@
         <v>5.449989</v>
       </c>
       <c r="N3" t="n">
-        <v>96.82461536661624</v>
+        <v>101.0710927332184</v>
       </c>
       <c r="O3" t="n">
-        <v>91.59820200002287</v>
+        <v>95.87047713333352</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01302440314145026</v>
+        <v>-0.001612021252883733</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.006501321612396915</v>
+        <v>-0.01582123522101836</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02280895412771028</v>
+        <v>0.002548299791322317</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01743603766827273</v>
+        <v>0.00140540532632949</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01835394238221522</v>
+        <v>0.005419445091831565</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E3_augmentation/results/results.xlsx
+++ b/experiments/E3_augmentation/results/results.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>default,flipud_on</t>
+          <t>default,rotate_30</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -588,11 +588,11 @@
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -740,10 +740,10 @@
         <v>5.449925</v>
       </c>
       <c r="N2" t="n">
-        <v>96.87502849992597</v>
+        <v>96.73597276663108</v>
       </c>
       <c r="O2" t="n">
-        <v>91.63380619993404</v>
+        <v>91.46305156670375</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -764,42 +764,42 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>flipud_on</t>
+          <t>rotate_30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vertical flip ON</t>
+          <t>rotation up to 30 degrees</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNREALISTIC: the road would be upside down, the camera never sees that</t>
+          <t>UNREALISTIC for a dashcam: the horizon is level; small tilts (a few degrees) are fine</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5215041216414924</v>
+        <v>0.4735694579748655</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2875122260258314</v>
+        <v>0.2372812568232848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6202798900142326</v>
+        <v>0.5602447277452063</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4782139192836582</v>
+        <v>0.4440049004074559</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4262987122974991</v>
+        <v>0.3866948330645856</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4520009086903073</v>
+        <v>0.3906568592516006</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5424219079827084</v>
+        <v>0.500135656235931</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6652949575954547</v>
+        <v>0.6167904833473449</v>
       </c>
       <c r="L3" t="n">
         <v>2.535344</v>
@@ -808,25 +808,25 @@
         <v>5.449989</v>
       </c>
       <c r="N3" t="n">
-        <v>101.0710927332184</v>
+        <v>112.2627140664918</v>
       </c>
       <c r="O3" t="n">
-        <v>95.87047713333352</v>
+        <v>106.046793733185</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.001612021252883733</v>
+        <v>-0.04954668491951064</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.01582123522101836</v>
+        <v>-0.05542511445393183</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002548299791322317</v>
+        <v>-0.05879574964738438</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00140540532632949</v>
+        <v>-0.04088084642044787</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005419445091831565</v>
+        <v>-0.04308502915627821</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E3_augmentation/results/results.xlsx
+++ b/experiments/E3_augmentation/results/results.xlsx
@@ -430,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>default,rotate_30</t>
+          <t>default,no_mosaic,no_hsv,no_fliplr,flipud_on,rotate_30</t>
         </is>
       </c>
     </row>
@@ -571,18 +571,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
@@ -590,10 +590,10 @@
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,10 +740,10 @@
         <v>5.449925</v>
       </c>
       <c r="N2" t="n">
-        <v>96.73597276663108</v>
+        <v>98.94005543307382</v>
       </c>
       <c r="O2" t="n">
-        <v>91.46305156670375</v>
+        <v>93.80501016645819</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -764,42 +764,42 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rotate_30</t>
+          <t>no_mosaic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>rotation up to 30 degrees</t>
+          <t>mosaic off</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNREALISTIC for a dashcam: the horizon is level; small tilts (a few degrees) are fine</t>
+          <t>mosaic glues 4 photos together: not a real road scene, but adds context variety</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4735694579748655</v>
+        <v>0.5206093987959717</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2372812568232848</v>
+        <v>0.2913628407137271</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5602447277452063</v>
+        <v>0.6076288085501791</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4440049004074559</v>
+        <v>0.4772154064750826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3866948330645856</v>
+        <v>0.4339497565715403</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3906568592516006</v>
+        <v>0.447627996336935</v>
       </c>
       <c r="J3" t="n">
-        <v>0.500135656235931</v>
+        <v>0.5473966397065639</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6167904833473449</v>
+        <v>0.6534632025688476</v>
       </c>
       <c r="L3" t="n">
         <v>2.535344</v>
@@ -808,24 +808,296 @@
         <v>5.449989</v>
       </c>
       <c r="N3" t="n">
-        <v>112.2627140664918</v>
+        <v>142.624894833231</v>
       </c>
       <c r="O3" t="n">
-        <v>106.046793733185</v>
+        <v>134.6622287336383</v>
       </c>
       <c r="P3" t="n">
+        <v>-0.002506744098404456</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.008170190946977185</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.001824612562049965</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.006380137050185031</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.006412309934775484</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>no_hsv</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>colour jitter off (hue/saturation/value)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>brightness/saturation changes are realistic (light, weather); strong hue shifts are not (blue asphalt)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5320690192742034</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2943072632765301</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.63170670153629</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4731630187037363</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4401527802054898</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4659027158372329</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5557851455163011</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6664354355377898</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.535344</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5.449925</v>
+      </c>
+      <c r="N4" t="n">
+        <v>115.3697022330865</v>
+      </c>
+      <c r="O4" t="n">
+        <v>108.4342840332586</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.008952876379827224</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.001967167313027707</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.01645010693824794</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01476864285992219</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.006559923034166748</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>no_fliplr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>horizontal flip off</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>left-right mirror is realistic (traffic side aside)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5361405460358264</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2991479711741394</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6405576329174778</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4821767001114827</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4356186259061205</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4722615630266953</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5584525403246516</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.6782294548858383</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.535344</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.449989</v>
+      </c>
+      <c r="N5" t="n">
+        <v>114.0087904670509</v>
+      </c>
+      <c r="O5" t="n">
+        <v>108.8502301667177</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.01302440314145026</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.006501321612396915</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.02280895412771028</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01743603766827273</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.01835394238221522</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>flipud_on</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>vertical flip ON</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UNREALISTIC: the road would be upside down, the camera never sees that</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5215041216414924</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2875122260258314</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6202798900142326</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4782139192836582</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4262987122974991</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4520009086903073</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5424219079827084</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6652949575954547</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.535344</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.449989</v>
+      </c>
+      <c r="N6" t="n">
+        <v>104.6844697998798</v>
+      </c>
+      <c r="O6" t="n">
+        <v>99.11655946640774</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.001612021252883733</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.01582123522101836</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.002548299791322317</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.00140540532632949</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.005419445091831565</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rotate_30</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rotation up to 30 degrees</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>UNREALISTIC for a dashcam: the horizon is level; small tilts (a few degrees) are fine</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4735694579748655</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2372812568232848</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5602447277452063</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4440049004074559</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3866948330645856</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3906568592516006</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.500135656235931</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6167904833473449</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.535344</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5.449989</v>
+      </c>
+      <c r="N7" t="n">
+        <v>131.9145782668178</v>
+      </c>
+      <c r="O7" t="n">
+        <v>124.617219266717</v>
+      </c>
+      <c r="P7" t="n">
         <v>-0.04954668491951064</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q7" t="n">
         <v>-0.05542511445393183</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R7" t="n">
         <v>-0.05879574964738438</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S7" t="n">
         <v>-0.04088084642044787</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T7" t="n">
         <v>-0.04308502915627821</v>
       </c>
     </row>
